--- a/CONDITIONS_2510_1910.xlsx
+++ b/CONDITIONS_2510_1910.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Условия участия" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Нормы — справка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="С площадок" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Условия участия'!$A$3:$R$57</definedName>
@@ -90,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -124,6 +125,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,12 +705,12 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>не требуется (в извещении не установлено) [пл.]</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>не требуется (в извещении не установлено) [пл.]</t>
         </is>
       </c>
       <c r="L4" s="5" t="inlineStr">
@@ -715,7 +725,7 @@
       </c>
       <c r="N4" s="5" t="inlineStr">
         <is>
-          <t>до 25.12.2026</t>
+          <t>срок исполнения контракта: с даты заключе… [пл.]</t>
         </is>
       </c>
       <c r="O4" s="5" t="inlineStr">
@@ -731,7 +741,7 @@
       <c r="Q4" s="7" t="n"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>ЗК: без торгов, побеждает мин. цена. Снижение ≥25% → обеспечение ×1,5.</t>
+          <t>Подробно — лист «С площадок». ЗК: без торгов, побеждает мин. цена. Снижение ≥25% → обеспечение ×1,5.</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1517,12 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>в извещении не установлено [пл.]</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>5.0% ≈ 24 810 ₽</t>
+          <t>5% — 24 810,00 руб. (ст.96 44-ФЗ) [пл.]</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
@@ -1527,7 +1537,7 @@
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>до 31.07.2027</t>
+          <t>срок исполнения контракта до 31.07.2027;… [пл.]</t>
         </is>
       </c>
       <c r="O14" s="5" t="inlineStr">
@@ -1545,7 +1555,7 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>ЗК: без торгов, побеждает мин. цена. Снижение ≥25% → обеспечение ×1,5.</t>
+          <t>Подробно — лист «С площадок». ЗК: без торгов, побеждает мин. цена. Снижение ≥25% → обеспечение ×1,5.</t>
         </is>
       </c>
     </row>
@@ -2399,32 +2409,32 @@
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>не требуется [пл.]</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>в извещении не требуется</t>
+          <t>не предусмотрено, кроме случая демпингово… [пл.]</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>не указан — см. проект договора</t>
+          <t>нет (обеспечение на возврат авансовых пла… [пл.]</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>≤ 7 раб. дн. после приёмки (ПП 1352)</t>
+          <t>безналичный расчет в течение 7 рабочих дн… [пл.]</t>
         </is>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>с момента заключения договора по 30.12.20… [пл.]</t>
         </is>
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>12 месяцев с момента поставки на склад, е… [пл.]</t>
         </is>
       </c>
       <c r="P25" s="5" t="inlineStr">
@@ -2435,7 +2445,7 @@
       <c r="Q25" s="7" t="n"/>
       <c r="R25" s="5" t="inlineStr">
         <is>
-          <t>Только МСП: обесп. заявки ≤2%, договора ≤5% (ПП 1352).</t>
+          <t>Подробно — лист «С площадок». Только МСП: обесп. заявки ≤2%, договора ≤5% (ПП 1352).</t>
         </is>
       </c>
     </row>
@@ -3283,17 +3293,17 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>1 005 499 ₽ (1.0%)</t>
+          <t>1 005 499,42 руб.; банковская гарантия ил… [пл.]</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>на возврат аванса: 100% аванса (БГ)</t>
+          <t>обеспечение возврата аванса не менее 100%… [пл.]</t>
         </is>
       </c>
       <c r="L36" s="9" t="inlineStr">
         <is>
-          <t>есть (см. документацию)</t>
+          <t>есть (в извещении ЕИС предусмотрено обесп… [пл.]</t>
         </is>
       </c>
       <c r="M36" s="5" t="inlineStr">
@@ -3319,7 +3329,11 @@
       <c r="Q36" s="10" t="n">
         <v>1005499.42</v>
       </c>
-      <c r="R36" s="5" t="inlineStr"/>
+      <c r="R36" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробно — лист «С площадок». </t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="48" customHeight="1">
       <c r="A37" s="4" t="n">
@@ -3605,12 +3619,12 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>в извещении ЕИС не указано [пл.]</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>≈ 13 644 ₽ (5.0%)</t>
+          <t>13 643,87 руб. (5% НМЦ), в соответствии с… [пл.]</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
@@ -3625,7 +3639,7 @@
       </c>
       <c r="N40" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>место: 630082, г. Новосибирск, ул. Жуковс… [пл.]</t>
         </is>
       </c>
       <c r="O40" s="5" t="inlineStr">
@@ -3639,11 +3653,11 @@
         </is>
       </c>
       <c r="Q40" s="7" t="n">
-        <v>13643.87</v>
+        <v>13643.868</v>
       </c>
       <c r="R40" s="5" t="inlineStr">
         <is>
-          <t>Только МСП: обесп. заявки ≤2%, договора ≤5% (ПП 1352).</t>
+          <t>Подробно — лист «С площадок». Только МСП: обесп. заявки ≤2%, договора ≤5% (ПП 1352).</t>
         </is>
       </c>
     </row>
@@ -3689,32 +3703,32 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>не установлено [пл.]</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>в извещении не требуется</t>
+          <t>не установлено (обеспечение гарантийных о… [пл.]</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>не указан — см. проект договора</t>
+          <t>нет (оплата после приемки) [пл.]</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>по договору (обычно 30–60 дн.)</t>
+          <t>не позднее 25 рабочих дней с даты приемки… [пл.]</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>в течение 10 рабочих дней с даты заключен… [пл.]</t>
         </is>
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>гарантийный срок завода-изготовителя; деф… [пл.]</t>
         </is>
       </c>
       <c r="P41" s="5" t="inlineStr">
@@ -3723,7 +3737,11 @@
         </is>
       </c>
       <c r="Q41" s="7" t="n"/>
-      <c r="R41" s="5" t="inlineStr"/>
+      <c r="R41" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробно — лист «С площадок». </t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="48" customHeight="1">
       <c r="A42" s="4" t="n">
@@ -4341,12 +4359,12 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>в извещении ЕИС не указано [пл.]</t>
         </is>
       </c>
       <c r="K49" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>72 000,00 руб.; путем внесения денежных с… [пл.]</t>
         </is>
       </c>
       <c r="L49" s="5" t="inlineStr">
@@ -4374,10 +4392,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="Q49" s="7" t="n"/>
+      <c r="Q49" s="7" t="n">
+        <v>72000</v>
+      </c>
       <c r="R49" s="5" t="inlineStr">
         <is>
-          <t>Извещение не загрузилось</t>
+          <t>Подробно — лист «С площадок». Извещение не загрузилось</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4607,32 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>6 420 573 ₽ (3.0%)</t>
+          <t>да, 3% НМЦД = 6 420 572,58 руб. [пл.]</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
-          <t>есть, размер — в Прил. к документации</t>
-        </is>
-      </c>
-      <c r="L52" s="9" t="inlineStr">
-        <is>
-          <t>есть (см. документацию)</t>
+          <t>да, 10% НМЦД (надлежащее исполнение); обе… [пл.]</t>
+        </is>
+      </c>
+      <c r="L52" s="5" t="inlineStr">
+        <is>
+          <t>нет (извещение п.13: оплата по факту пост… [пл.]</t>
         </is>
       </c>
       <c r="M52" s="5" t="inlineStr">
         <is>
-          <t>по договору (обычно 30–60 дн.)</t>
+          <t>по факту поставки в течение 30 рабочих дн… [пл.]</t>
         </is>
       </c>
       <c r="N52" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>партиями по заявкам Покупателя, даты пост… [пл.]</t>
         </is>
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>72 месяца с момента поставки (1333 позици… [пл.]</t>
         </is>
       </c>
       <c r="P52" s="5" t="inlineStr">
@@ -4621,9 +4641,13 @@
         </is>
       </c>
       <c r="Q52" s="10" t="n">
-        <v>6420572.58</v>
-      </c>
-      <c r="R52" s="5" t="inlineStr"/>
+        <v>27822481.177</v>
+      </c>
+      <c r="R52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробно — лист «С площадок». </t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="48" customHeight="1">
       <c r="A53" s="4" t="n">
@@ -4667,12 +4691,12 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>не требуется</t>
+          <t>в извещении ЕИС не указано [пл.]</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>≈ 95 697 ₽ (10.0%)</t>
+          <t>95 697,06 руб. (10% НМЦ); до заключения д… [пл.]</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
@@ -4687,7 +4711,7 @@
       </c>
       <c r="N53" s="5" t="inlineStr">
         <is>
-          <t>по документации</t>
+          <t>место и срок — по ТЗ и проекту договора (… [пл.]</t>
         </is>
       </c>
       <c r="O53" s="5" t="inlineStr">
@@ -4703,7 +4727,11 @@
       <c r="Q53" s="7" t="n">
         <v>95697.06</v>
       </c>
-      <c r="R53" s="5" t="inlineStr"/>
+      <c r="R53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Подробно — лист «С площадок». </t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="48" customHeight="1">
       <c r="A54" s="4" t="n">
@@ -5267,4 +5295,551 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Номер</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="inlineStr">
+        <is>
+          <t>Предмет</t>
+        </is>
+      </c>
+      <c r="C1" s="12" t="inlineStr">
+        <is>
+          <t>Аванс</t>
+        </is>
+      </c>
+      <c r="D1" s="12" t="inlineStr">
+        <is>
+          <t>Оплата</t>
+        </is>
+      </c>
+      <c r="E1" s="12" t="inlineStr">
+        <is>
+          <t>Срок/место поставки</t>
+        </is>
+      </c>
+      <c r="F1" s="12" t="inlineStr">
+        <is>
+          <t>Обеспечение заявки</t>
+        </is>
+      </c>
+      <c r="G1" s="12" t="inlineStr">
+        <is>
+          <t>Обеспечение договора</t>
+        </is>
+      </c>
+      <c r="H1" s="12" t="inlineStr">
+        <is>
+          <t>Гарантия</t>
+        </is>
+      </c>
+      <c r="I1" s="12" t="inlineStr">
+        <is>
+          <t>Прочее</t>
+        </is>
+      </c>
+      <c r="J1" s="12" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="200" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>0352500002526000089</t>
+        </is>
+      </c>
+      <c r="B2" s="14" t="inlineStr">
+        <is>
+          <t>Поставка спецодежды и обуви (Реестровый номер 2026.066998)</t>
+        </is>
+      </c>
+      <c r="C2" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr">
+        <is>
+          <t>срок исполнения контракта: с даты заключения по 25.12.2026; место: Омская обл., Большереченский р-н, рп. Большеречье, ул. Дорожная, д. 27</t>
+        </is>
+      </c>
+      <c r="F2" s="14" t="inlineStr">
+        <is>
+          <t>не требуется (в извещении не установлено)</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr">
+        <is>
+          <t>не требуется (в извещении не установлено)</t>
+        </is>
+      </c>
+      <c r="H2" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>Заказчик БУ «Тевризское ДРСУ»; ЗК, НМЦК 498 211,82 руб., собственные средства; запрет на иностранные товары (нацрежим) по всем позициям; преимущество организациям инвалидов 15%; позиции: костюмы зимние (44+5), ботинки утепленные (51 пар), костюм сварщика зимний (2); окончание подачи 26.10.2026 08:00 (Омск), итоги 28.10.2026; ЭТП РТС-тендер. Аванс/срок оплаты — только в Проекте контракта (файл в ЕИС, недоступен)</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
+          <t>https://v2test.gosplan.info/fz44/purchases/0352500002526000089/notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="200" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>0325300007726000124</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>Поставка расходных материалов для КДЛ (пробирки лот 2)</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>срок исполнения контракта до 31.07.2027; место: г. Астрахань, ул. Украинская, зд. 5</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>в извещении не установлено</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>5% — 24 810,00 руб. (ст.96 44-ФЗ)</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>Заказчик ГБУЗ АО «Городская поликлиника №5»; Поставка расходных материалов для КДЛ (пробирки лот 2), 30 000 шт., НМЦК 496 200 руб.; запрет на иностранные товары; преимущество организациям инвалидов 15%; окончание подачи 26.10.2026 09:00 (Астрахань), итоги 28.10.2026. Аванс/оплата — в проекте контракта (недоступен)</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
+          <t>https://v2test.gosplan.info/fz44/purchases/0325300007726000124/notification</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="200" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>32616451568</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Поставка запорной арматуры для нужд филиала ПАО «Россети Центр и Приволжье» - «Удмуртэнер…</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>нет (обеспечение на возврат авансовых платежей не предусмотрено; оплата после поставки)</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>безналичный расчет в течение 7 рабочих дней с момента подписания накладной, предоставления счета-фактуры и иных документов (ПП №1352)</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>с момента заключения договора по 30.12.2026 по заявкам Покупателя; поставка в течение 10 календарных дней с момента подачи заявки; DDP склад филиала «Удмуртэнерго», г. Ижевск, ул. Воткинское шоссе, 105</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>не требуется</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>не предусмотрено, кроме случая демпинговой цены (снижение ≥25% от НМЦ); обеспечение гарантийных обязательств не предусмотрено</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>12 месяцев с момента поставки на склад, если изготовителем не установлен больший</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>ЗК МСП, РАД (tender.lot-online.ru); частичное выполнение поставок не допускается; нацрежим — ограничение; Уведомление №1 от 19.10.2026: окончание подачи 26.10.2026 10:00 МСК, итоги 27.10.2026; место — Удмуртская Республика</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>https://tender.lot-online.ru/app/OfferCard/page?OfferCard.offerUUID=Ssmsptb19718u80000q27s1it1atgot2c (документация ОЗК МСП, ТЗ, уведомление №1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="200" customHeight="1">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>32616346943</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>ОКПД2 28.14.13 Поставка трубопроводной арматуры среднего, низкого давления и механизмов у…</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>есть (в извещении ЕИС предусмотрено обеспечение возврата предварительной оплаты (аванса) — не менее 100% размера аванса); размер аванса — в проекте договора (не получен)</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>1 005 499,42 руб.; банковская гарантия или денежные средства на реквизиты ЭТП</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>обеспечение возврата аванса не менее 100% уплачиваемого аванса (с учетом ранее выплаченных непогашенных авансов); иные требования к обеспечению исполнения — в проекте договора (Прил.2)</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Конкурс в эл. форме (не МСП), Лот № 0200-РЕМ ПРОД-2027-КамчЭн, ЭТП rushydro.roseltorg.ru; место поставки Камчатский край (несколько грузополучателей/филиалов); нацрежим — ограничение; 4 редакции извещения (посл. 13.10.2026), окончание подачи по документации до 29.10.2026; в разъяснениях — обязательность записи в реестре Минпромторга, сертификатов/деклараций ТР ТС. Документация (Прил.2 Проект договора) лежит только в ЕИС/Росэлторг — недоступны</t>
+        </is>
+      </c>
+      <c r="J5" s="14" t="inlineStr">
+        <is>
+          <t>https://v2test.gosplan.info/fz223/purchases/32616346943 (зеркало данных ЕИС, ГосПлан API); roseltorg.ru недоступен</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="200" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>32616481886</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Поставка оборудования и материалов</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>место: 630082, г. Новосибирск, ул. Жуковского, 98</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>в извещении ЕИС не указано</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>13 643,87 руб. (5% НМЦ), в соответствии с документацией</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>ЗК МСП (Извещение №41К-2026), ГАУ ССО НСО «Новосибирский дом ветеранов», поставка оборудования и материалов, НМЦ 272 877,36; нацрежим: ограничение/запрет/исключения; окончание подачи 26.10.2026 10:00; РТС-тендер</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>https://v2test.gosplan.info/fz223/purchases/32616481886</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="200" customHeight="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>32616477841</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>поставка электроматериалов</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>нет (оплата после приемки)</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>не позднее 25 рабочих дней с даты приемки товара, подписания товарно-сопроводительных документов и выставления счета</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>в течение 10 рабочих дней с даты заключения договора; г. Луганск, ул. Филатова, 79 (транспортом поставщика, с разгрузкой)</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>не установлено</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>не установлено (обеспечение гарантийных обязательств не требуется)</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
+        <is>
+          <t>гарантийный срок завода-изготовителя; дефекты устраняются в течение 10 дней (по ряду позиций ТЗ указан гарантийный срок эксплуатации 10 лет, напр. арматура СИП)</t>
+        </is>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Заказчик МУП «ЛУГАНСКГОРСВЕТ» (ЛНР); ЗК в эл. форме на ЭТП ООО «РЭСТ» (etp.r-est.ru); НМЦ 485 643 руб.; не только МСП; цена фиксированная</t>
+        </is>
+      </c>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t>https://etp.r-est.ru/app/OfferCard/page?OfferCard.offerUUID=Scorebobgvmb580000q2gpjfvrq6i4qog (Извещение, Проект договора, ТЗ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="200" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>32616484613</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>ОРЭСВО-4080 Поставка материалов для выполнения обязательств по договорам технологического…</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t>в извещении ЕИС не указано</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>72 000,00 руб.; путем внесения денежных средств на счет Заказчика или независимой гарантии</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Заказчик АО «ОРЭС-Владимирская область»; материалы для техприсоединения; конкурс в эл. форме только МСП; ЭТП corp.roseltorg.ru (notice 837546); место — Владимирская обл.; нацрежим: ограничение по части позиций + преимущество; окончание подачи 27.10.2026 10:00; документация архивом ОРЭСВО-4080.7z в ЕИС</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t>https://v2test.gosplan.info/fz223/purchases/32616484613</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="200" customHeight="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>32616480459</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Определение поставщика на поставку кабельно-проводниковой продукции на напряжение до 1 кВ…</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>нет (извещение п.13: оплата по факту поставки; Прил.4 «Условия выбора фин. обеспечения»: обеспечение на возврат аванса — Нет). Проект договора содержит оба варианта (без аванса / с авансом ___%), но извещение устанавливает оплату по факту</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>по факту поставки в течение 30 рабочих дней; для субъектов МСП — 7 рабочих дней (со дня подписания ТОРГ-12/УПД)</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>партиями по заявкам Покупателя, даты поставки по позициям в спецификации с 20.01.2027 по 15.12.2027 (основные даты 01.02, 01.04, 01.06, 31.08.2027); по договору поставка в течение 3 календарных дней от направления подписанной Заявки, если иной срок не указан в Заявке</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>да, 3% НМЦД = 6 420 572,58 руб.</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>да, 10% НМЦД (надлежащее исполнение); обеспечение гарантийных обязательств 5% от цены договора (Прил.4)</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
+        <is>
+          <t>72 месяца с момента поставки (1333 позиции), 66 месяцев (198 позиций); по проекту договора — 36 мес. если больший не указан</t>
+        </is>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>Конкурс в эл. форме, не МСП; нацрежим: ОГРАНИЧЕНИЕ (ПП 1875) для 1333 поз., ПРЕИМУЩЕСТВО для 198; требуется аттестация ПАО «Россети»; толеранс по длине ±5%; получатели — филиалы МВС, ЗЭС, МКС, СЭС, ВЭС, Новая Москва, ЮЭС (Москва и МО); переторжка предусмотрена (шаг 0,08%); подача до 02.11.2026 10:00 МСК, итоги до 25.11.2026</t>
+        </is>
+      </c>
+      <c r="J9" s="14" t="inlineStr">
+        <is>
+          <t>https://tender.lot-online.ru/app/OfferCard/page?OfferCard.offerUUID=Sgpmspc19718u80000q2h5ag2nkgrmlis (архив документации RAD: Извещение, Прил.4, Прил.2 Договор, Спецификация 062-0010777)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="200" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>32616478568</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Поставка силового бронированного кабеля для городского электрифицированного транспорта АС…</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>место и срок — по ТЗ и проекту договора (не получены)</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>в извещении ЕИС не указано</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>95 697,06 руб. (10% НМЦ); до заключения договора; независимая гарантия или деньги на счет Заказчика; возврат в течение 30 дней после исполнения обязательств</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>Аукцион в эл. форме (не МСП-only), МУП «Коломенский трамвай», кабель АСБ 1х800+2х1,5-1кВ, 300 м, НМЦ 956 970,60; нацрежим — ограничение; окончание подачи 02.11.2026 10:00; РТС-тендер/ЕАСУЗ МО (недоступны); проект «Умный договор» в ЕИС</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>https://v2test.gosplan.info/fz223/purchases/32616478568</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>